--- a/statistics_tables/variety_protein_results.xlsx
+++ b/statistics_tables/variety_protein_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">location</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t xml:space="preserve">groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSD</t>
   </si>
   <si>
     <t xml:space="preserve">mean_group_se</t>
@@ -509,19 +515,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>2022</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>12.5592143171802</v>
@@ -530,33 +542,39 @@
         <v>0.0434802069712473</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.00000000000756192120843671</v>
       </c>
       <c r="I2" t="n">
+        <v>0.114396804026188</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.309448540093389</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>12.4534290031275</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0248484606139944</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>12.1848081915997</v>
@@ -565,33 +583,39 @@
         <v>0.0316192753351808</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.00000000000756192120843671</v>
       </c>
       <c r="I3" t="n">
+        <v>0.114396804026188</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.309448540093389</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>12.4534290031275</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.0248484606139944</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>12.6162645006026</v>
@@ -600,33 +624,39 @@
         <v>0.045854248936468</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00000000000756192120843671</v>
       </c>
       <c r="I4" t="n">
+        <v>0.114396804026188</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.309448540093389</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>12.4534290031275</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.0248484606139944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>12.8743985304571</v>
@@ -635,33 +665,39 @@
         <v>0.0609156885543322</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00142563254326627</v>
       </c>
       <c r="I5" t="n">
+        <v>0.160164720307136</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.36135020611522</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>12.8636134723242</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.0280908787326872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>13.0088310405008</v>
@@ -670,33 +706,39 @@
         <v>0.0542199212845408</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00142563254326627</v>
       </c>
       <c r="I6" t="n">
+        <v>0.160164720307136</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.36135020611522</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>12.8636134723242</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.0280908787326872</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>12.7076108460148</v>
@@ -705,33 +747,39 @@
         <v>0.0560064655576303</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.00142563254326627</v>
       </c>
       <c r="I7" t="n">
+        <v>0.160164720307136</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.36135020611522</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>12.8636134723242</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0280908787326872</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>11.4712249068829</v>
@@ -740,33 +788,37 @@
         <v>0.0607199662726116</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.110107469218813</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.427077977430529</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>11.3861956084465</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0375083998305557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>11.4193955823357</v>
@@ -775,33 +827,37 @@
         <v>0.0667590542458238</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.110107469218813</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.427077977430529</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>11.3861956084465</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0375083998305557</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>11.2679663361209</v>
@@ -810,33 +866,37 @@
         <v>0.0819025334224684</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.110107469218813</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.427077977430529</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>11.3861956084465</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.0375083998305557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>11.9995366596376</v>
@@ -845,33 +905,39 @@
         <v>0.0813388781076512</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0266474038619611</v>
       </c>
       <c r="I11" t="n">
+        <v>0.295444791480381</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.648226615050324</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>11.7674361386324</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.0550864782620064</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>11.6158847983728</v>
@@ -880,33 +946,39 @@
         <v>0.125746949162327</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0266474038619611</v>
       </c>
       <c r="I12" t="n">
+        <v>0.295444791480381</v>
+      </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.648226615050324</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>11.7674361386324</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.0550864782620064</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>11.6868869578869</v>
@@ -915,33 +987,39 @@
         <v>0.104280343534118</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0266474038619611</v>
       </c>
       <c r="I13" t="n">
+        <v>0.295444791480381</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.648226615050324</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>11.7674361386324</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.0550864782620064</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>10.9820850573474</v>
@@ -950,33 +1028,39 @@
         <v>0.0460045737695147</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0223122951552478</v>
       </c>
       <c r="I14" t="n">
+        <v>0.123928786043554</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.272368640551373</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>10.9459059771373</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.0248831518487613</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>11.0097995407313</v>
@@ -985,33 +1069,39 @@
         <v>0.0492353003419188</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0223122951552478</v>
       </c>
       <c r="I15" t="n">
+        <v>0.123928786043554</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.272368640551373</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>10.9459059771373</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.0248831518487613</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>10.8458333333333</v>
@@ -1020,33 +1110,39 @@
         <v>0.0363195146286007</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0223122951552478</v>
       </c>
       <c r="I16" t="n">
+        <v>0.123928786043554</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.272368640551373</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>10.9459059771373</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0248831518487613</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" t="n">
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>12.0925339939314</v>
@@ -1055,33 +1151,39 @@
         <v>0.0452585754684347</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.000000573086373538347</v>
       </c>
       <c r="I17" t="n">
+        <v>0.124282767395838</v>
+      </c>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.302073895154665</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>12.0322224348972</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0251054114723275</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" t="n">
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>12.1745401891062</v>
@@ -1090,33 +1192,39 @@
         <v>0.0478041754182988</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.000000573086373538347</v>
       </c>
       <c r="I18" t="n">
+        <v>0.124282767395838</v>
+      </c>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.302073895154665</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>12.0322224348972</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0251054114723275</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" t="n">
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>11.829593121654</v>
@@ -1125,33 +1233,39 @@
         <v>0.0394916047778559</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>37</v>
+        <v>19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.000000573086373538347</v>
       </c>
       <c r="I19" t="n">
+        <v>0.124282767395838</v>
+      </c>
+      <c r="J19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.302073895154665</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>12.0322224348972</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.0251054114723275</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>11.9563937072983</v>
@@ -1160,33 +1274,39 @@
         <v>0.0315812294007097</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.00000000000000000265881914048564</v>
       </c>
       <c r="I20" t="n">
+        <v>0.0932293341595276</v>
+      </c>
+      <c r="J20" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.290531520058945</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>11.922600410121</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.0243681336340279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>12.163679905876</v>
@@ -1195,33 +1315,39 @@
         <v>0.0356415716186595</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.00000000000000000265881914048564</v>
       </c>
       <c r="I21" t="n">
+        <v>0.0932293341595276</v>
+      </c>
+      <c r="J21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.290531520058945</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>11.922600410121</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.0243681336340279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>11.6477276171888</v>
@@ -1230,33 +1356,39 @@
         <v>0.0323795786071299</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.00000000000000000265881914048564</v>
       </c>
       <c r="I22" t="n">
+        <v>0.0932293341595276</v>
+      </c>
+      <c r="J22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.290531520058945</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>11.922600410121</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.0243681336340279</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="n">
         <v>2024</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>9.185</v>
@@ -1265,33 +1397,39 @@
         <v>0.0449964725248829</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.000285812135063727</v>
       </c>
       <c r="I23" t="n">
+        <v>0.125996328078428</v>
+      </c>
+      <c r="J23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.28864647549529</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>9.06481481481481</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0318425121077542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" t="n">
         <v>2024</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>9.08833333333333</v>
@@ -1300,33 +1438,39 @@
         <v>0.0552332715463631</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>43</v>
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.000285812135063727</v>
       </c>
       <c r="I24" t="n">
+        <v>0.125996328078428</v>
+      </c>
+      <c r="J24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.28864647549529</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9.06481481481481</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.0318425121077542</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" t="n">
         <v>2024</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>8.92111111111111</v>
@@ -1335,18 +1479,24 @@
         <v>0.0313271974178982</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" t="s">
-        <v>44</v>
+        <v>19</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.000285812135063727</v>
       </c>
       <c r="I25" t="n">
+        <v>0.125996328078428</v>
+      </c>
+      <c r="J25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.28864647549529</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>9.06481481481481</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0318425121077542</v>
       </c>
     </row>
